--- a/Sprint_Review_Protocol_1.xlsx
+++ b/Sprint_Review_Protocol_1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florian\Desktop\itp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sebastianmatuszyk/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{83C73FB7-F60C-4C68-948D-CA6E2647D350}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF3EF30-8670-844A-BD45-235704D13BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{5C77D34F-34C3-4D2F-849C-09193AE86D67}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17120" xr2:uid="{5C77D34F-34C3-4D2F-849C-09193AE86D67}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -119,9 +119,6 @@
     <t>Room 1 designed</t>
   </si>
   <si>
-    <t>Object research</t>
-  </si>
-  <si>
     <t>Basic AI</t>
   </si>
   <si>
@@ -138,15 +135,25 @@
   </si>
   <si>
     <t>Transfer your estimate as well as your real effort from your planing tool to this protocol</t>
+  </si>
+  <si>
+    <t>Object research, classroom filled</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -382,94 +389,94 @@
   </cellStyleXfs>
   <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -485,9 +492,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -525,7 +532,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -631,7 +638,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -773,7 +780,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -782,41 +789,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AE3C726-37E9-451B-9308-D99ECF6E7468}">
   <dimension ref="A1:I31"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="8" style="2" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.42578125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.42578125" style="2"/>
-    <col min="8" max="8" width="34.5703125" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="11.42578125" style="2"/>
+    <col min="2" max="2" width="32.6640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.5" style="2"/>
+    <col min="8" max="8" width="34.5" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="11.5" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="29"/>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
     </row>
     <row r="3" spans="1:9" ht="27" thickBot="1">
       <c r="A3" s="5"/>
@@ -830,133 +837,133 @@
       <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="26" t="s">
+      <c r="A4" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="18">
+      <c r="B4" s="22"/>
+      <c r="C4" s="23">
         <v>1</v>
       </c>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="19"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="24"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="30">
+      <c r="B5" s="13"/>
+      <c r="C5" s="25">
         <v>46102</v>
       </c>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="21"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="27"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="20">
+      <c r="B6" s="13"/>
+      <c r="C6" s="26">
         <v>35</v>
       </c>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20"/>
-      <c r="G6" s="21"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="27"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="31" t="s">
+      <c r="B7" s="13"/>
+      <c r="C7" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="23"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="30"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="32" t="s">
+      <c r="B8" s="13"/>
+      <c r="C8" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="25"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="20"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="32" t="s">
+      <c r="B9" s="13"/>
+      <c r="C9" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="25"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="20"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="32" t="s">
+      <c r="B10" s="13"/>
+      <c r="C10" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="25"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="20"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="33" t="s">
+      <c r="B11" s="13"/>
+      <c r="C11" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="11"/>
-    </row>
-    <row r="12" spans="1:9" ht="16.5" thickBot="1">
-      <c r="A12" s="16" t="s">
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="33"/>
+    </row>
+    <row r="12" spans="1:9" ht="17" thickBot="1">
+      <c r="A12" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="12" t="s">
+      <c r="B12" s="15"/>
+      <c r="C12" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="13"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="11"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
+      <c r="B14" s="16"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
@@ -997,7 +1004,7 @@
       <c r="D16" s="7">
         <v>3</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="2">
         <f>D16-C16</f>
         <v>-2</v>
       </c>
@@ -1018,7 +1025,7 @@
       <c r="D17" s="7">
         <v>7</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="2">
         <f t="shared" ref="E17:E25" si="0">D17-C17</f>
         <v>2</v>
       </c>
@@ -1030,18 +1037,18 @@
       <c r="A18" s="8">
         <v>3</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>27</v>
+      <c r="B18" s="9" t="s">
+        <v>33</v>
       </c>
       <c r="C18" s="7">
         <v>5</v>
       </c>
       <c r="D18" s="7">
-        <v>6</v>
-      </c>
-      <c r="E18" s="9">
+        <v>7</v>
+      </c>
+      <c r="E18" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="4"/>
@@ -1052,13 +1059,13 @@
         <v>4</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" s="7">
         <v>5</v>
       </c>
       <c r="D19" s="7"/>
-      <c r="E19" s="9">
+      <c r="E19" s="2">
         <f t="shared" si="0"/>
         <v>-5</v>
       </c>
@@ -1071,7 +1078,7 @@
         <v>5</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20" s="7">
         <v>5</v>
@@ -1079,7 +1086,7 @@
       <c r="D20" s="7">
         <v>3</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="2">
         <f t="shared" si="0"/>
         <v>-2</v>
       </c>
@@ -1094,7 +1101,7 @@
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
-      <c r="E21" s="9">
+      <c r="E21" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1109,7 +1116,7 @@
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
-      <c r="E22" s="9">
+      <c r="E22" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1119,12 +1126,12 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
-      <c r="E23" s="9">
+      <c r="E23" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1134,12 +1141,12 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
-      <c r="E24" s="9">
+      <c r="E24" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1149,12 +1156,12 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
-      <c r="E25" s="9">
+      <c r="E25" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1172,7 +1179,7 @@
       <c r="D26" s="6"/>
       <c r="E26" s="6">
         <f>SUM(E16:E25)</f>
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="F26" s="6">
         <f>COUNT(F16:F25)</f>
@@ -1187,17 +1194,16 @@
     <row r="30" spans="1:8">
       <c r="A30" s="7"/>
       <c r="B30" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="B31" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="C9:G9"/>
     <mergeCell ref="C10:G10"/>
@@ -1212,11 +1218,12 @@
     <mergeCell ref="C6:G6"/>
     <mergeCell ref="C7:G7"/>
     <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C11:G11"/>
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Sprint_Review_Protocol_1.xlsx
+++ b/Sprint_Review_Protocol_1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29917"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sebastianmatuszyk/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF3EF30-8670-844A-BD45-235704D13BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{210A369C-252D-4AAB-A170-15757BC3C983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17120" xr2:uid="{5C77D34F-34C3-4D2F-849C-09193AE86D67}"/>
   </bookViews>
@@ -119,7 +119,10 @@
     <t>Room 1 designed</t>
   </si>
   <si>
-    <t>Basic AI</t>
+    <t>Object research, classroom filled</t>
+  </si>
+  <si>
+    <t>Basic Enemy AI</t>
   </si>
   <si>
     <t>Crouch function</t>
@@ -135,9 +138,6 @@
   </si>
   <si>
     <t>Transfer your estimate as well as your real effort from your planing tool to this protocol</t>
-  </si>
-  <si>
-    <t>Object research, classroom filled</t>
   </si>
 </sst>
 </file>
@@ -391,21 +391,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -420,19 +420,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -441,42 +450,33 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -492,9 +492,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -532,7 +532,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -638,7 +638,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -780,7 +780,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -788,159 +788,178 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AE3C726-37E9-451B-9308-D99ECF6E7468}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:I31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15.95"/>
   <cols>
     <col min="1" max="1" width="8" style="2" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.83203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="11.5" style="2"/>
-    <col min="8" max="8" width="34.5" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="11.5" style="2"/>
+    <col min="2" max="2" width="32.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="11.42578125" style="2"/>
+    <col min="8" max="8" width="34.42578125" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" spans="1:9" ht="27" thickBot="1">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="23">
+      <c r="B4" s="25"/>
+      <c r="C4" s="26">
         <v>1</v>
       </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="24"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="12" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="13"/>
-      <c r="C5" s="25">
+      <c r="C5" s="28">
         <v>46102</v>
       </c>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="27"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="12" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="13"/>
-      <c r="C6" s="26">
+      <c r="C6" s="29">
         <v>35</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="27"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="12" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="13"/>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="30"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="33"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="12" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="13"/>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="20"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="12" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="13"/>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="20"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="12" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="13"/>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="20"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="12" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="13"/>
-      <c r="C11" s="31" t="s">
+      <c r="C11" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="33"/>
-    </row>
-    <row r="12" spans="1:9" ht="17" thickBot="1">
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+    </row>
+    <row r="12" spans="1:9" ht="17.100000000000001" thickBot="1">
       <c r="A12" s="14" t="s">
         <v>14</v>
       </c>
@@ -952,6 +971,8 @@
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="11"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="16" t="s">
@@ -964,6 +985,7 @@
       <c r="F14" s="16"/>
       <c r="G14" s="16"/>
       <c r="H14" s="16"/>
+      <c r="I14" s="5"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
@@ -990,217 +1012,234 @@
       <c r="H15" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="I15" s="5"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="8">
+      <c r="A16" s="6">
         <v>1</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="3">
         <v>5</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="3">
         <v>3</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="5">
         <f>D16-C16</f>
         <v>-2</v>
       </c>
-      <c r="F16" s="3"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="5"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="8">
+      <c r="A17" s="6">
         <v>2</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="3">
         <v>5</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="3">
         <v>7</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="5">
         <f t="shared" ref="E17:E25" si="0">D17-C17</f>
         <v>2</v>
       </c>
-      <c r="F17" s="3"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="3"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="8">
+      <c r="A18" s="6">
         <v>3</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="7">
+      <c r="B18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="3">
         <v>5</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="3">
         <v>7</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="3"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="8">
+      <c r="A19" s="6">
         <v>4</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="7">
+      <c r="B19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="3">
         <v>5</v>
       </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="2">
-        <f t="shared" si="0"/>
-        <v>-5</v>
-      </c>
-      <c r="F19" s="3"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="8">
-        <v>5</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="7">
-        <v>5</v>
-      </c>
-      <c r="D20" s="7">
+      <c r="D19" s="3">
         <v>3</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E19" s="5">
         <f t="shared" si="0"/>
         <v>-2</v>
       </c>
-      <c r="F20" s="3"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="6">
+        <v>5</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="3">
+        <v>5</v>
+      </c>
+      <c r="D20" s="3">
+        <v>3</v>
+      </c>
+      <c r="E20" s="5">
+        <f t="shared" si="0"/>
+        <v>-2</v>
+      </c>
+      <c r="F20" s="7"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="3"/>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="8">
+      <c r="A21" s="6">
         <v>6</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="2">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="3"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="8">
+      <c r="A22" s="6">
         <v>7</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="2">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="3"/>
     </row>
     <row r="23" spans="1:8">
-      <c r="A23" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="2">
+      <c r="A23" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="3"/>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="2">
+      <c r="A24" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="3"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="2">
+      <c r="A25" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="5">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="3"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="6">
+      <c r="A26" s="9">
         <f>COUNT(A16:A25)</f>
         <v>7</v>
       </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6">
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9">
         <f>SUM(E16:E25)</f>
-        <v>-5</v>
-      </c>
-      <c r="F26" s="6">
+        <v>-2</v>
+      </c>
+      <c r="F26" s="9">
         <f>COUNT(F16:F25)</f>
         <v>0</v>
       </c>
-      <c r="G26" s="6">
+      <c r="G26" s="9">
         <f>COUNT(G16:G25)</f>
         <v>0</v>
       </c>
-      <c r="H26" s="6"/>
+      <c r="H26" s="9"/>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="7"/>
-      <c r="B30" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="A30" s="3"/>
+      <c r="B30" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
     </row>
     <row r="31" spans="1:8">
-      <c r="B31" s="2" t="s">
-        <v>32</v>
-      </c>
+      <c r="A31" s="5"/>
+      <c r="B31" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -1226,6 +1265,6 @@
     <mergeCell ref="C11:G11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToWidth="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>